--- a/UploadTemplates/addQuestionnaireTemplate.xlsx
+++ b/UploadTemplates/addQuestionnaireTemplate.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\john\Desktop\hs3MVC_Latest\Generic\uploadedFiles\Questionnaire\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\standard\genericlatest1\Generic\UploadTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>

--- a/UploadTemplates/addQuestionnaireTemplate.xlsx
+++ b/UploadTemplates/addQuestionnaireTemplate.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Page</t>
   </si>
@@ -120,6 +120,9 @@
   </si>
   <si>
     <t>UploadMessageText</t>
+  </si>
+  <si>
+    <t>CalendarMessageText</t>
   </si>
 </sst>
 </file>
@@ -771,7 +774,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z82"/>
+  <dimension ref="A1:AA82"/>
   <sheetFormatPr defaultColWidth="10.28515625" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="13" bestFit="1" customWidth="1"/>
@@ -794,12 +797,13 @@
     <col min="18" max="18" width="18.7109375" style="13" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="17" style="13" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="29.140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="24.28515625" style="13" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.5703125" style="13" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="10.28515625" style="13"/>
+    <col min="21" max="21" width="29.140625" style="13" customWidth="1"/>
+    <col min="22" max="22" width="24.28515625" style="13" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="10.28515625" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" s="8" t="s">
         <v>14</v>
       </c>
@@ -861,25 +865,28 @@
         <v>28</v>
       </c>
       <c r="U1" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="V1" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="V1" s="8" t="s">
+      <c r="W1" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="W1" s="28" t="s">
+      <c r="X1" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="X1" s="8" t="s">
+      <c r="Y1" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="Y1" s="30" t="s">
+      <c r="Z1" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="Z1" s="30" t="s">
+      <c r="AA1" s="30" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2" s="14"/>
       <c r="C2" s="15"/>
       <c r="E2" s="5"/>
@@ -897,9 +904,10 @@
       <c r="S2" s="31"/>
       <c r="T2" s="12"/>
       <c r="U2" s="12"/>
-      <c r="V2" s="20"/>
-    </row>
-    <row r="3" spans="1:26">
+      <c r="V2" s="12"/>
+      <c r="W2" s="20"/>
+    </row>
+    <row r="3" spans="1:27">
       <c r="A3" s="14"/>
       <c r="C3" s="15"/>
       <c r="E3" s="6"/>
@@ -917,9 +925,10 @@
       <c r="S3" s="12"/>
       <c r="T3" s="12"/>
       <c r="U3" s="12"/>
-      <c r="V3" s="20"/>
-    </row>
-    <row r="4" spans="1:26">
+      <c r="V3" s="12"/>
+      <c r="W3" s="20"/>
+    </row>
+    <row r="4" spans="1:27">
       <c r="A4" s="14"/>
       <c r="C4" s="15"/>
       <c r="E4" s="3"/>
@@ -937,9 +946,10 @@
       <c r="S4" s="12"/>
       <c r="T4" s="12"/>
       <c r="U4" s="12"/>
-      <c r="V4" s="20"/>
-    </row>
-    <row r="5" spans="1:26" ht="14.25">
+      <c r="V4" s="12"/>
+      <c r="W4" s="20"/>
+    </row>
+    <row r="5" spans="1:27" ht="14.25">
       <c r="A5" s="14"/>
       <c r="C5" s="15"/>
       <c r="E5" s="4"/>
@@ -957,9 +967,10 @@
       <c r="S5" s="12"/>
       <c r="T5" s="12"/>
       <c r="U5" s="12"/>
-      <c r="V5" s="20"/>
-    </row>
-    <row r="6" spans="1:26">
+      <c r="V5" s="12"/>
+      <c r="W5" s="20"/>
+    </row>
+    <row r="6" spans="1:27">
       <c r="A6" s="14"/>
       <c r="C6" s="15"/>
       <c r="E6" s="3"/>
@@ -975,7 +986,7 @@
       <c r="O6" s="19"/>
       <c r="P6" s="19"/>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:27">
       <c r="A7" s="14"/>
       <c r="C7" s="15"/>
       <c r="E7" s="3"/>
@@ -993,9 +1004,10 @@
       <c r="S7" s="12"/>
       <c r="T7" s="12"/>
       <c r="U7" s="12"/>
-      <c r="V7" s="20"/>
-    </row>
-    <row r="8" spans="1:26">
+      <c r="V7" s="12"/>
+      <c r="W7" s="20"/>
+    </row>
+    <row r="8" spans="1:27">
       <c r="A8" s="14"/>
       <c r="C8" s="15"/>
       <c r="E8" s="3"/>
@@ -1013,9 +1025,10 @@
       <c r="S8" s="12"/>
       <c r="T8" s="12"/>
       <c r="U8" s="12"/>
-      <c r="V8" s="20"/>
-    </row>
-    <row r="9" spans="1:26">
+      <c r="V8" s="12"/>
+      <c r="W8" s="20"/>
+    </row>
+    <row r="9" spans="1:27">
       <c r="A9" s="14"/>
       <c r="C9" s="15"/>
       <c r="E9" s="3"/>
@@ -1033,9 +1046,10 @@
       <c r="S9" s="12"/>
       <c r="T9" s="12"/>
       <c r="U9" s="12"/>
-      <c r="V9" s="20"/>
-    </row>
-    <row r="10" spans="1:26">
+      <c r="V9" s="12"/>
+      <c r="W9" s="20"/>
+    </row>
+    <row r="10" spans="1:27">
       <c r="A10" s="14"/>
       <c r="C10" s="15"/>
       <c r="E10" s="3"/>
@@ -1053,9 +1067,10 @@
       <c r="S10" s="12"/>
       <c r="T10" s="12"/>
       <c r="U10" s="12"/>
-      <c r="V10" s="20"/>
-    </row>
-    <row r="11" spans="1:26">
+      <c r="V10" s="12"/>
+      <c r="W10" s="20"/>
+    </row>
+    <row r="11" spans="1:27">
       <c r="A11" s="14"/>
       <c r="C11" s="15"/>
       <c r="E11" s="3"/>
@@ -1073,9 +1088,10 @@
       <c r="S11" s="12"/>
       <c r="T11" s="12"/>
       <c r="U11" s="12"/>
-      <c r="V11" s="20"/>
-    </row>
-    <row r="12" spans="1:26">
+      <c r="V11" s="12"/>
+      <c r="W11" s="20"/>
+    </row>
+    <row r="12" spans="1:27">
       <c r="A12" s="14"/>
       <c r="C12" s="15"/>
       <c r="E12" s="3"/>
@@ -1093,9 +1109,10 @@
       <c r="S12" s="31"/>
       <c r="T12" s="12"/>
       <c r="U12" s="12"/>
-      <c r="V12" s="20"/>
-    </row>
-    <row r="13" spans="1:26">
+      <c r="V12" s="12"/>
+      <c r="W12" s="20"/>
+    </row>
+    <row r="13" spans="1:27">
       <c r="A13" s="14"/>
       <c r="C13" s="15"/>
       <c r="E13" s="3"/>
@@ -1111,7 +1128,7 @@
       <c r="O13" s="19"/>
       <c r="P13" s="19"/>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:27">
       <c r="A14" s="14"/>
       <c r="C14" s="15"/>
       <c r="E14" s="3"/>
@@ -1127,7 +1144,7 @@
       <c r="O14" s="19"/>
       <c r="P14" s="19"/>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:27">
       <c r="A15" s="14"/>
       <c r="C15" s="22"/>
       <c r="E15" s="3"/>
@@ -1143,7 +1160,7 @@
       <c r="O15" s="19"/>
       <c r="P15" s="19"/>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:27">
       <c r="A16" s="14"/>
       <c r="C16" s="22"/>
       <c r="E16" s="3"/>
@@ -2184,17 +2201,17 @@
       <c r="P82" s="19"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="T1">
+  <conditionalFormatting sqref="T1:U1">
     <cfRule type="expression" dxfId="2" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U1">
+  <conditionalFormatting sqref="V1">
     <cfRule type="expression" dxfId="1" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W1">
+  <conditionalFormatting sqref="X1">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>

--- a/UploadTemplates/addQuestionnaireTemplate.xlsx
+++ b/UploadTemplates/addQuestionnaireTemplate.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Page</t>
   </si>
@@ -126,13 +126,16 @@
   </si>
   <si>
     <t>SubCheckBoxChoice</t>
+  </si>
+  <si>
+    <t>NarrativeHint</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="宋体"/>
@@ -155,6 +158,12 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="5">
@@ -195,7 +204,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -231,6 +240,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -619,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AC1"/>
   <sheetFormatPr defaultColWidth="10.28515625" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="7" bestFit="1" customWidth="1"/>
@@ -649,7 +661,7 @@
     <col min="25" max="16384" width="10.28515625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28">
+    <row r="1" spans="1:29">
       <c r="A1" s="3" t="s">
         <v>14</v>
       </c>
@@ -733,6 +745,9 @@
       </c>
       <c r="AB1" s="13" t="s">
         <v>27</v>
+      </c>
+      <c r="AC1" s="14" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
